--- a/data/excel/Administration_AvenueManagement_BusinessUnit.xlsx
+++ b/data/excel/Administration_AvenueManagement_BusinessUnit.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA3CB86-B115-490D-A3D3-5BC53D05CFC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BFE40AE-82F1-4DEF-B2B3-AB6352798E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -66,27 +66,15 @@
     <t>qlabs12345</t>
   </si>
   <si>
-    <t>Verify Corporate Profiling</t>
-  </si>
-  <si>
     <t>BUName</t>
   </si>
   <si>
-    <t>Test1</t>
-  </si>
-  <si>
     <t>BUCode</t>
   </si>
   <si>
-    <t>T001</t>
-  </si>
-  <si>
     <t>BUAddress</t>
   </si>
   <si>
-    <t>720,JMD</t>
-  </si>
-  <si>
     <t>BUContry</t>
   </si>
   <si>
@@ -108,10 +96,22 @@
     <t>del</t>
   </si>
   <si>
-    <t>Password@123</t>
-  </si>
-  <si>
-    <t>Piyush_QL</t>
+    <t>Piyush_ql</t>
+  </si>
+  <si>
+    <t>EE6B4B@E7</t>
+  </si>
+  <si>
+    <t>721,JMD</t>
+  </si>
+  <si>
+    <t>Verify Businnes Unit details</t>
+  </si>
+  <si>
+    <t>Test7</t>
+  </si>
+  <si>
+    <t>T007</t>
   </si>
 </sst>
 </file>
@@ -205,9 +205,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -524,26 +528,26 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="L1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>21</v>
+      <c r="N1" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -551,7 +555,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>8</v>
@@ -562,41 +566,50 @@
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
-      </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="M2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>"at,qlabs12345"</formula1>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{138CBA9E-7887-4508-9F9F-B3177CC702E0}">
+      <formula1>"EE6B4B@E7,07DE6@EAB,F1CD@9E4B"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{624A6E23-3A02-47C5-8107-320A8941111E}">
+      <formula1>"at,qlabs12345,merg123456"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{C03B279A-97A4-4C92-8CBC-A1AB656C81F9}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{789391A3-C7D5-4A9B-B60F-1A0141CEEC6E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>